--- a/data/project_standards/00_reference/reference_dataset.xlsx
+++ b/data/project_standards/00_reference/reference_dataset.xlsx
@@ -291,8 +291,8 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="tb_ref_sdg_observed_mapping" displayName="tb_ref_sdg_observed_mapping" ref="A1:C1" headerRowCount="1">
-  <autoFilter ref="A1:C1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="tb_ref_sdg_observed_mapping" displayName="tb_ref_sdg_observed_mapping" ref="A1:C18" headerRowCount="1">
+  <autoFilter ref="A1:C18"/>
   <tableColumns count="3">
     <tableColumn id="1" name="sdg_raw"/>
     <tableColumn id="2" name="observed_count"/>
@@ -303,7 +303,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tb_ref_standards_status" displayName="tb_ref_standards_status" ref="A1:G85" headerRowCount="1" headerRowDxfId="22" dataDxfId="21" totalsRowDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tb_ref_standards_status" displayName="tb_ref_standards_status" ref="A1:G87" headerRowCount="1" headerRowDxfId="22" dataDxfId="21" totalsRowDxfId="20">
   <autoFilter ref="A1:G80"/>
   <tableColumns count="7">
     <tableColumn id="1" name="standard_acronym" dataDxfId="19"/>
@@ -3348,7 +3348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -3371,6 +3371,227 @@
         <is>
           <t>sdg_goal_id</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Goal 13: Climate Action</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>4058</v>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Goal 7: Affordable and Clean Energy</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>2680</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Goal 8: Decent Work and Economic Growth</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>2411</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Goal 3: Good Health and Well-Being</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>2229</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Goal 5: Gender Equality</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>1562</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Goal 15: Life On Land</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>1183</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Goal 6: Clean Water and Sanitation</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>1006</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Goal 1: No Poverty</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>1004</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Goal 12: Responsible Production and Consumption</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>559</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Goal 4: Quality Education</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>515</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Goal 9: Industry, Innovation and Infrastructure</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>274</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Goal 2: Zero Hunger</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>213</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Goal 17: Partnerships for the Goals</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>108</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Goal 11: Sustainable Cities and Communities</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>76</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Goal 10: Reduced Inequalities</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Goal 14: Life Below Water</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Goal 16: Peace, Justice and Strong Institutions</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -3387,7 +3608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="45.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="21.5546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6501,6 +6722,40 @@
       <c r="G85" t="inlineStr">
         <is>
           <t>REG</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>BCR</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>voluntary</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Registration Request Under Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>EQE</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>voluntary</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Issuance and Transfer</t>
         </is>
       </c>
     </row>

--- a/data/project_standards/00_reference/reference_dataset.xlsx
+++ b/data/project_standards/00_reference/reference_dataset.xlsx
@@ -291,8 +291,8 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="tb_ref_sdg_observed_mapping" displayName="tb_ref_sdg_observed_mapping" ref="A1:C18" headerRowCount="1">
-  <autoFilter ref="A1:C18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="tb_ref_sdg_observed_mapping" displayName="tb_ref_sdg_observed_mapping" ref="A1:C7" headerRowCount="1">
+  <autoFilter ref="A1:C7"/>
   <tableColumns count="3">
     <tableColumn id="1" name="sdg_raw"/>
     <tableColumn id="2" name="observed_count"/>
@@ -3348,7 +3348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -3376,50 +3376,50 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Goal 13: Climate Action</t>
+          <t>09: Industry, Innovation and Infrastructure</t>
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>4058</v>
+        <v>15</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Goal 7: Affordable and Clean Energy</t>
+          <t>13: Climate Action</t>
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>2680</v>
+        <v>15</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Goal 8: Decent Work and Economic Growth</t>
+          <t>12: Responsible Consumption and Production</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>2411</v>
+        <v>14</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Goal 3: Good Health and Well-Being</t>
+          <t>03: Good Health and Well-Being</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>2229</v>
+        <v>1</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>3</v>
@@ -3428,170 +3428,27 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Goal 5: Gender Equality</t>
+          <t>06: Clean Water and Sanitation</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1562</v>
+        <v>1</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Goal 15: Life On Land</t>
+          <t>15: Life on Land</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>1183</v>
+        <v>1</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>15</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Goal 6: Clean Water and Sanitation</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n">
-        <v>1006</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Goal 1: No Poverty</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n">
-        <v>1004</v>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Goal 12: Responsible Production and Consumption</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>559</v>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Goal 4: Quality Education</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>515</v>
-      </c>
-      <c r="C11" s="7" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Goal 9: Industry, Innovation and Infrastructure</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>274</v>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Goal 2: Zero Hunger</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>213</v>
-      </c>
-      <c r="C13" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Goal 17: Partnerships for the Goals</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n">
-        <v>108</v>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Goal 11: Sustainable Cities and Communities</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n">
-        <v>76</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Goal 10: Reduced Inequalities</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="C16" s="7" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Goal 14: Life Below Water</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="C17" s="7" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Goal 16: Peace, Justice and Strong Institutions</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
